--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486929_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486929_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.888</v>
+        <v>5.8029</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4003</v>
+        <v>2.9891</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4877</v>
+        <v>2.8138</v>
       </c>
       <c r="G2" t="n">
         <v>2.7465</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9755</v>
+        <v>-1.0606</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4337</v>
+        <v>-0.8448</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.2157</v>
       </c>
       <c r="V2" t="n">
         <v>3.2957</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1888</v>
+        <v>4.4778</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8841</v>
+        <v>2.0545</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3047</v>
+        <v>2.4233</v>
       </c>
       <c r="G3" t="n">
         <v>2.1003</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6527</v>
+        <v>-1.3637</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2516</v>
+        <v>-1.0811</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4012</v>
+        <v>-0.2826</v>
       </c>
       <c r="V3" t="n">
         <v>3.5359</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4484</v>
+        <v>3.1995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5107</v>
+        <v>-0.3534</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9377</v>
+        <v>3.5528</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2119</v>
+        <v>4.0963</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5677</v>
+        <v>2.3778</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6442</v>
+        <v>1.7185</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3055</v>
+        <v>2.5216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4774</v>
+        <v>1.7588</v>
       </c>
       <c r="L4" t="n">
-        <v>0.828</v>
+        <v>0.7629</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9064</v>
+        <v>1.5747</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.6191</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8161</v>
+        <v>0.9556</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7991</v>
+        <v>-0.4861</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4806</v>
+        <v>-0.6162</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2797</v>
+        <v>0.1301</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4021</v>
+        <v>2.6669</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.21</v>
+        <v>0.2627</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6121</v>
+        <v>2.4041</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0963</v>
+        <v>2.2119</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3778</v>
+        <v>0.5677</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7185</v>
+        <v>1.6442</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5216</v>
+        <v>1.3055</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7588</v>
+        <v>0.4774</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7629</v>
+        <v>0.828</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5747</v>
+        <v>0.9064</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6191</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9556</v>
+        <v>0.8161</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2835</v>
+        <v>0.0176</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4729</v>
+        <v>-0.7286</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1894</v>
+        <v>0.7461</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.0349</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0563</v>
+        <v>1.0176</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1605</v>
+        <v>0.0173</v>
       </c>
       <c r="G6" t="n">
         <v>2.5603</v>
@@ -922,13 +922,13 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2108</v>
+        <v>-0.0717</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3912</v>
+        <v>0.3524</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.602</v>
+        <v>-0.4241</v>
       </c>
       <c r="V6" t="n">
         <v>-1.6591</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7703</v>
+        <v>0.3239</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.9093</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4704</v>
+        <v>1.2332</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4312</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1398</v>
+        <v>0.6935</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5888</v>
+        <v>0.3796</v>
       </c>
       <c r="U7" t="n">
-        <v>0.551</v>
+        <v>0.3139</v>
       </c>
       <c r="V7" t="n">
         <v>0.2402</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3268</v>
+        <v>-0.6563</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3238</v>
+        <v>-0.7422</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.003</v>
+        <v>0.0859</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7386</v>
@@ -1078,13 +1078,13 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2065</v>
+        <v>-0.123</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2362</v>
+        <v>-0.1822</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0298</v>
+        <v>0.0592</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5217</v>
+        <v>-1.2532</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1762</v>
+        <v>-2.967</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6545</v>
+        <v>1.7138</v>
       </c>
       <c r="G9" t="n">
         <v>1.4448</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.2421</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8409</v>
+        <v>-0.6317</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3303</v>
+        <v>0.3895</v>
       </c>
       <c r="V9" t="n">
         <v>0.8295</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3681</v>
+        <v>-5.8904</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0928</v>
+        <v>-3.6744</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2753</v>
+        <v>-2.2161</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1088</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0376</v>
+        <v>-0.5599</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7091</v>
+        <v>-0.2907</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3285</v>
+        <v>-0.2692</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6591</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.376699999999998</v>
+        <v>9.706000000000003</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6515</v>
+        <v>-2.3224</v>
       </c>
       <c r="F11" t="n">
-        <v>12.0283</v>
+        <v>12.0281</v>
       </c>
       <c r="G11" t="n">
         <v>7.881500000000002</v>
@@ -1312,13 +1312,13 @@
         <v>12.3205</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.525300000000001</v>
+        <v>-3.196</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.972599999999999</v>
+        <v>-3.6433</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4471000000000002</v>
+        <v>0.4471999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>3.9938</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7169</v>
+        <v>3.884</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3469</v>
+        <v>2.7895</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3699</v>
+        <v>1.0944</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4872</v>
+        <v>2.2343</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0501</v>
+        <v>0.8396</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5629</v>
+        <v>1.3947</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5524</v>
+        <v>3.3748</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9076</v>
+        <v>0.9149</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3552</v>
+        <v>2.4599</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-1.1405</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1425</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2077</v>
+        <v>-1.0652</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4107</v>
+        <v>2.0534</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2564</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7514</v>
+        <v>-0.6551</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5049</v>
+        <v>1.3601</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7679</v>
+        <v>-0.6982</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2484</v>
+        <v>0.4805</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4805</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3916</v>
+        <v>3.5268</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9527</v>
+        <v>2.9285</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4389</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2343</v>
+        <v>0.4872</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8396</v>
+        <v>2.0501</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3947</v>
+        <v>-1.5629</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3748</v>
+        <v>0.5524</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9149</v>
+        <v>1.9076</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4599</v>
+        <v>-1.3552</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1405</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.1425</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0652</v>
+        <v>-0.2077</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0534</v>
+        <v>0.4107</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7873</v>
+        <v>1.0664</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4919</v>
+        <v>0.333</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7046</v>
+        <v>0.7333</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6982</v>
+        <v>1.7679</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4805</v>
+        <v>2.2484</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4031</v>
+        <v>1.2043</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0004</v>
+        <v>0.1877</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5972</v>
+        <v>1.0166</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8944</v>
+        <v>-0.0056</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2653</v>
+        <v>-0.5159</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3709</v>
+        <v>0.5104</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1519</v>
+        <v>1.072</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1519</v>
+        <v>-0.6905</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2575</v>
+        <v>-1.0776</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1134</v>
+        <v>0.1746</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3709</v>
+        <v>-1.2522</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R14" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0365</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5733</v>
+        <v>-0.2211</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4631</v>
+        <v>0.7266</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4805</v>
+        <v>-0.4579</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4189</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4601</v>
+        <v>0.819</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.034</v>
+        <v>1.5819</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4941</v>
+        <v>-0.7629</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3536</v>
+        <v>0.8944</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3438</v>
+        <v>1.2653</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6974</v>
+        <v>-0.3709</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2954</v>
+        <v>1.1519</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2954</v>
+        <v>1.1519</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0582</v>
+        <v>-0.2575</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6392</v>
+        <v>0.1134</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6974</v>
+        <v>-0.3709</v>
       </c>
       <c r="P15" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5095</v>
+        <v>0.4524</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3294</v>
+        <v>0.1549</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1801</v>
+        <v>0.2974</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.9384</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2501</v>
+        <v>0.6083</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3164</v>
+        <v>-0.034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5665</v>
+        <v>0.6423</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1277</v>
+        <v>0.3536</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2171</v>
+        <v>-0.3438</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3448</v>
+        <v>0.6974</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7609</v>
+        <v>0.2954</v>
       </c>
       <c r="K16" t="n">
-        <v>0.419</v>
+        <v>0.2954</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3418</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6332</v>
+        <v>0.0582</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6362</v>
+        <v>-0.6392</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.997</v>
+        <v>0.6974</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7035</v>
+        <v>-0.3613</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1117</v>
+        <v>-0.3294</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5918</v>
+        <v>-0.0319</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9384</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3334</v>
+        <v>-1.4481</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7537</v>
+        <v>-1.3624</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4204</v>
+        <v>-0.0856</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0056</v>
+        <v>0.1277</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5159</v>
+        <v>-0.2171</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5104</v>
+        <v>0.3448</v>
       </c>
       <c r="J17" t="n">
-        <v>1.072</v>
+        <v>1.7609</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6905</v>
+        <v>0.419</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7626</v>
+        <v>1.3418</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0776</v>
+        <v>-1.6332</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1746</v>
+        <v>-0.6362</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2522</v>
+        <v>-0.997</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6427</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2053</v>
+        <v>-3.0801</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0322</v>
+        <v>1.0054</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1625</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1304</v>
+        <v>0.9397</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9384</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4579</v>
+        <v>-0.1088</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4805</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4765</v>
+        <v>-1.6857</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5752</v>
+        <v>-1.7844</v>
       </c>
       <c r="F18" t="n">
         <v>0.0987</v>
@@ -1858,10 +1858,10 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.86</v>
+        <v>0.6508</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4144</v>
+        <v>0.2051</v>
       </c>
       <c r="U18" t="n">
         <v>0.4457</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5386</v>
+        <v>-2.6589</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5071</v>
+        <v>-2.7163</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0315</v>
+        <v>0.0574</v>
       </c>
       <c r="G19" t="n">
         <v>-3.9344</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7798</v>
+        <v>0.6595</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8096</v>
+        <v>0.6004</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0298</v>
+        <v>0.0592</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>-4.6477</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5315</v>
+        <v>-4.9499</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1162</v>
+        <v>0.3022</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8371</v>
@@ -2017,10 +2017,10 @@
         <v>0.1976</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.159</v>
+        <v>-0.5774</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3566</v>
+        <v>0.775</v>
       </c>
       <c r="V20" t="n">
         <v>-2.0082</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.6022</v>
+        <v>-6.8867</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.6104</v>
+        <v>-8.668900000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0081</v>
+        <v>1.7823</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5159</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9795</v>
+        <v>0.7361</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9649</v>
+        <v>-0.0235</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0146</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.376600000000002</v>
+        <v>-7.2847</v>
       </c>
       <c r="E22" t="n">
         <v>-12.0283</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6517</v>
+        <v>4.7437</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.881400000000001</v>
+        <v>-7.881399999999999</v>
       </c>
       <c r="H22" t="n">
         <v>2.9198</v>
@@ -2155,10 +2155,10 @@
         <v>-5.9784</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6523</v>
+        <v>-0.6522999999999998</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.325999999999999</v>
+        <v>-5.326</v>
       </c>
       <c r="P22" t="n">
         <v>-1.0268</v>
@@ -2170,13 +2170,13 @@
         <v>11.2939</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5253</v>
+        <v>5.6175</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4473000000000003</v>
+        <v>-0.4474</v>
       </c>
       <c r="U22" t="n">
-        <v>3.9726</v>
+        <v>6.0647</v>
       </c>
       <c r="V22" t="n">
         <v>-3.9939</v>
